--- a/basedatos_partidas/salida/descompuestos/07.02.01.080.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.02.01.080.xlsx
@@ -584,10 +584,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H11" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>114.54</v>
+        <v>104.54</v>
       </c>
     </row>
     <row r="15">
@@ -795,10 +795,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>136.11</v>
+        <v>126.11</v>
       </c>
       <c r="H23" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="24">
@@ -814,7 +814,7 @@
       </c>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="5" t="n">
-        <v>137.47</v>
+        <v>127.37</v>
       </c>
     </row>
   </sheetData>
